--- a/data/Mar/21-03-2026/NGAY 21-03.xlsx
+++ b/data/Mar/21-03-2026/NGAY 21-03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\21-03-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74B2A0D-ECFA-422C-8C25-093D1AFF64DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82AF1C6D-9073-4BCA-9120-74029F862CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -589,20 +589,20 @@
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -928,55 +928,55 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="5" t="s">
         <v>16</v>
       </c>
     </row>
@@ -993,16 +993,16 @@
       <c r="E3" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>7</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>890</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>30</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="6">
         <f>G3-H3</f>
         <v>860</v>
       </c>
@@ -1015,7 +1015,7 @@
       <c r="L3" t="s">
         <v>23</v>
       </c>
-      <c r="Q3" s="7">
+      <c r="Q3" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1035,13 +1035,13 @@
       <c r="F4" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>1325</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>25</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="6">
         <f>G4-H4</f>
         <v>1300</v>
       </c>
@@ -1054,7 +1054,7 @@
       <c r="L4" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="Q4" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1074,13 +1074,13 @@
       <c r="F5" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <v>765</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="6">
         <v>25</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="6">
         <f>G5-H5</f>
         <v>740</v>
       </c>
@@ -1093,7 +1093,7 @@
       <c r="L5" t="s">
         <v>23</v>
       </c>
-      <c r="Q5" s="7">
+      <c r="Q5" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1110,16 +1110,16 @@
       <c r="E6" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <v>8</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="6">
         <v>0</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="6">
         <v>25</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="6">
         <f>-H6</f>
         <v>-25</v>
       </c>
@@ -1132,7 +1132,7 @@
       <c r="L6" t="s">
         <v>23</v>
       </c>
-      <c r="Q6" s="7">
+      <c r="Q6" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1149,16 +1149,16 @@
       <c r="E7" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>7</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <v>670</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="6">
         <v>30</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="6">
         <f>G7-H7</f>
         <v>640</v>
       </c>
@@ -1171,7 +1171,7 @@
       <c r="L7" t="s">
         <v>23</v>
       </c>
-      <c r="Q7" s="7">
+      <c r="Q7" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1191,13 +1191,13 @@
       <c r="F8" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="6">
         <v>890</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="6">
         <v>30</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="6">
         <f>G8-H8</f>
         <v>860</v>
       </c>
@@ -1210,7 +1210,7 @@
       <c r="L8" t="s">
         <v>23</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="Q8" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1230,13 +1230,13 @@
       <c r="F9" t="s">
         <v>72</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="6">
         <v>2010</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="6">
         <v>30</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="6">
         <f>G9-H9</f>
         <v>1980</v>
       </c>
@@ -1249,7 +1249,7 @@
       <c r="L9" t="s">
         <v>23</v>
       </c>
-      <c r="Q9" s="7">
+      <c r="Q9" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1269,13 +1269,13 @@
       <c r="F10" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="6">
         <v>405</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="6">
         <v>25</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="6">
         <f>G10-H10</f>
         <v>380</v>
       </c>
@@ -1288,7 +1288,7 @@
       <c r="L10" t="s">
         <v>23</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="Q10" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1308,13 +1308,13 @@
       <c r="F11" t="s">
         <v>72</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="6">
         <v>0</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="6">
         <v>25</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="6">
         <f>-H11</f>
         <v>-25</v>
       </c>
@@ -1327,7 +1327,7 @@
       <c r="L11" t="s">
         <v>23</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q11" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1347,13 +1347,13 @@
       <c r="F12" t="s">
         <v>72</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="6">
         <v>610</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="6">
         <v>30</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="6">
         <f>G12-H12</f>
         <v>580</v>
       </c>
@@ -1366,7 +1366,7 @@
       <c r="L12" t="s">
         <v>23</v>
       </c>
-      <c r="Q12" s="7">
+      <c r="Q12" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1386,13 +1386,13 @@
       <c r="F13" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="6">
         <v>380</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="6">
         <v>30</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="6">
         <f>G13-H13</f>
         <v>350</v>
       </c>
@@ -1405,7 +1405,7 @@
       <c r="L13" t="s">
         <v>23</v>
       </c>
-      <c r="Q13" s="7">
+      <c r="Q13" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1425,13 +1425,13 @@
       <c r="F14" t="s">
         <v>108</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="6">
         <v>625</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="6">
         <v>35</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="6">
         <f>G14-H14</f>
         <v>590</v>
       </c>
@@ -1444,7 +1444,7 @@
       <c r="L14" t="s">
         <v>23</v>
       </c>
-      <c r="Q14" s="7">
+      <c r="Q14" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1461,16 +1461,16 @@
       <c r="E15" t="s">
         <v>111</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="6">
         <v>8</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="6">
         <v>405</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="6">
         <v>25</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="6">
         <f>G15-H15</f>
         <v>380</v>
       </c>
@@ -1483,7 +1483,7 @@
       <c r="L15" t="s">
         <v>23</v>
       </c>
-      <c r="Q15" s="7">
+      <c r="Q15" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1503,13 +1503,13 @@
       <c r="F16" t="s">
         <v>115</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="6">
         <v>995</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="6">
         <v>35</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="6">
         <f>G16-H16</f>
         <v>960</v>
       </c>
@@ -1522,7 +1522,7 @@
       <c r="L16" t="s">
         <v>23</v>
       </c>
-      <c r="Q16" s="7">
+      <c r="Q16" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1539,16 +1539,16 @@
       <c r="E17" t="s">
         <v>118</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="6">
         <v>7</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="6">
         <v>0</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="6">
         <v>30</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="6">
         <f>-H17</f>
         <v>-30</v>
       </c>
@@ -1564,7 +1564,7 @@
       <c r="M17" t="s">
         <v>119</v>
       </c>
-      <c r="Q17" s="7">
+      <c r="Q17" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1584,13 +1584,13 @@
       <c r="F18" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="6">
         <v>975</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="6">
         <v>25</v>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="6">
         <f>G18-H18</f>
         <v>950</v>
       </c>
@@ -1603,7 +1603,7 @@
       <c r="L18" t="s">
         <v>23</v>
       </c>
-      <c r="Q18" s="7">
+      <c r="Q18" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1623,13 +1623,13 @@
       <c r="F19" t="s">
         <v>42</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="6">
         <v>600</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="6">
         <v>20</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="6">
         <f>G19-H19</f>
         <v>580</v>
       </c>
@@ -1642,7 +1642,7 @@
       <c r="L19" t="s">
         <v>23</v>
       </c>
-      <c r="Q19" s="7">
+      <c r="Q19" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1662,13 +1662,13 @@
       <c r="F20" t="s">
         <v>42</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="6">
         <v>660</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="6">
         <v>20</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I20" s="6">
         <f>G20-H20</f>
         <v>640</v>
       </c>
@@ -1681,7 +1681,7 @@
       <c r="L20" t="s">
         <v>23</v>
       </c>
-      <c r="Q20" s="7">
+      <c r="Q20" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1698,16 +1698,16 @@
       <c r="E21" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="6">
         <v>2</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="6">
         <v>750</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="6">
         <v>30</v>
       </c>
-      <c r="I21" s="7">
+      <c r="I21" s="6">
         <f>G21-H21</f>
         <v>720</v>
       </c>
@@ -1720,7 +1720,7 @@
       <c r="L21" t="s">
         <v>23</v>
       </c>
-      <c r="Q21" s="7">
+      <c r="Q21" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1737,16 +1737,16 @@
       <c r="E22" t="s">
         <v>58</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="6">
         <v>2</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="6">
         <v>0</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="6">
         <v>30</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="6">
         <f>-H22</f>
         <v>-30</v>
       </c>
@@ -1759,7 +1759,7 @@
       <c r="L22" t="s">
         <v>23</v>
       </c>
-      <c r="Q22" s="7">
+      <c r="Q22" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1779,13 +1779,13 @@
       <c r="F23" t="s">
         <v>34</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="6">
         <v>745</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="6">
         <v>25</v>
       </c>
-      <c r="I23" s="7">
+      <c r="I23" s="6">
         <f>G23-H23</f>
         <v>720</v>
       </c>
@@ -1798,7 +1798,7 @@
       <c r="L23" t="s">
         <v>23</v>
       </c>
-      <c r="Q23" s="7">
+      <c r="Q23" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1818,13 +1818,13 @@
       <c r="F24" t="s">
         <v>34</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="6">
         <v>755</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="6">
         <v>25</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I24" s="6">
         <f>G24-H24</f>
         <v>730</v>
       </c>
@@ -1837,7 +1837,7 @@
       <c r="L24" t="s">
         <v>23</v>
       </c>
-      <c r="Q24" s="7">
+      <c r="Q24" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1857,13 +1857,13 @@
       <c r="F25" t="s">
         <v>88</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="6">
         <v>520</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25" s="6">
         <v>30</v>
       </c>
-      <c r="I25" s="7">
+      <c r="I25" s="6">
         <f>G25-H25</f>
         <v>490</v>
       </c>
@@ -1876,7 +1876,7 @@
       <c r="L25" t="s">
         <v>23</v>
       </c>
-      <c r="Q25" s="7">
+      <c r="Q25" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1893,16 +1893,16 @@
       <c r="E26" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="7">
-        <v>1</v>
-      </c>
-      <c r="G26" s="7">
+      <c r="F26" s="6">
+        <v>1</v>
+      </c>
+      <c r="G26" s="6">
         <v>365</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="6">
         <v>25</v>
       </c>
-      <c r="I26" s="7">
+      <c r="I26" s="6">
         <f>G26-H26</f>
         <v>340</v>
       </c>
@@ -1915,7 +1915,7 @@
       <c r="L26" t="s">
         <v>23</v>
       </c>
-      <c r="Q26" s="7">
+      <c r="Q26" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1932,16 +1932,16 @@
       <c r="E27" t="s">
         <v>30</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="6">
         <v>10</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="6">
         <v>785</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="6">
         <v>25</v>
       </c>
-      <c r="I27" s="7">
+      <c r="I27" s="6">
         <f>G27-H27</f>
         <v>760</v>
       </c>
@@ -1954,7 +1954,7 @@
       <c r="L27" t="s">
         <v>23</v>
       </c>
-      <c r="Q27" s="7">
+      <c r="Q27" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1974,13 +1974,13 @@
       <c r="F28" t="s">
         <v>38</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="6">
         <v>0</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="6">
         <v>25</v>
       </c>
-      <c r="I28" s="7">
+      <c r="I28" s="6">
         <f>-H28</f>
         <v>-25</v>
       </c>
@@ -1993,7 +1993,7 @@
       <c r="L28" t="s">
         <v>23</v>
       </c>
-      <c r="Q28" s="7">
+      <c r="Q28" s="6">
         <v>1</v>
       </c>
     </row>
@@ -2013,13 +2013,13 @@
       <c r="F29" t="s">
         <v>68</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="6">
         <v>0</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="6">
         <v>20</v>
       </c>
-      <c r="I29" s="7">
+      <c r="I29" s="6">
         <f>-H29</f>
         <v>-20</v>
       </c>
@@ -2032,7 +2032,7 @@
       <c r="L29" t="s">
         <v>23</v>
       </c>
-      <c r="Q29" s="7">
+      <c r="Q29" s="6">
         <v>1</v>
       </c>
     </row>
@@ -2052,13 +2052,13 @@
       <c r="F30" t="s">
         <v>68</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="6">
         <v>610</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H30" s="6">
         <v>20</v>
       </c>
-      <c r="I30" s="7">
+      <c r="I30" s="6">
         <f>G30-H30</f>
         <v>590</v>
       </c>
@@ -2071,7 +2071,7 @@
       <c r="L30" t="s">
         <v>23</v>
       </c>
-      <c r="Q30" s="7">
+      <c r="Q30" s="6">
         <v>1</v>
       </c>
     </row>
@@ -2091,13 +2091,13 @@
       <c r="F31" t="s">
         <v>38</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="6">
         <v>0</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31" s="6">
         <v>25</v>
       </c>
-      <c r="I31" s="7">
+      <c r="I31" s="6">
         <f>-H31</f>
         <v>-25</v>
       </c>
@@ -2110,7 +2110,7 @@
       <c r="L31" t="s">
         <v>23</v>
       </c>
-      <c r="Q31" s="7">
+      <c r="Q31" s="6">
         <v>1</v>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
       <c r="E32" t="s">
         <v>122</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="6">
         <v>5</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32" s="6">
         <v>0</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H32" s="6">
         <v>30</v>
       </c>
-      <c r="I32" s="7">
+      <c r="I32" s="6">
         <f>-H32</f>
         <v>-30</v>
       </c>
@@ -2149,7 +2149,7 @@
       <c r="L32" t="s">
         <v>23</v>
       </c>
-      <c r="Q32" s="7">
+      <c r="Q32" s="6">
         <v>1</v>
       </c>
     </row>
@@ -2166,16 +2166,16 @@
       <c r="E33" t="s">
         <v>124</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="6">
         <v>4</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G33" s="6">
         <v>30</v>
       </c>
-      <c r="H33" s="7">
+      <c r="H33" s="6">
         <v>30</v>
       </c>
-      <c r="I33" s="7">
+      <c r="I33" s="6">
         <f>G33-H33</f>
         <v>0</v>
       </c>
@@ -2188,7 +2188,7 @@
       <c r="L33" t="s">
         <v>23</v>
       </c>
-      <c r="Q33" s="7">
+      <c r="Q33" s="6">
         <v>1</v>
       </c>
     </row>
@@ -2208,13 +2208,13 @@
       <c r="F34" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="7">
+      <c r="G34" s="6">
         <v>40</v>
       </c>
-      <c r="H34" s="7">
+      <c r="H34" s="6">
         <v>40</v>
       </c>
-      <c r="I34" s="7">
+      <c r="I34" s="6">
         <f>G34-H34</f>
         <v>0</v>
       </c>
@@ -2227,104 +2227,104 @@
       <c r="L34" t="s">
         <v>23</v>
       </c>
-      <c r="Q34" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" s="15" t="s">
+      <c r="Q34" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="10">
         <v>12</v>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="10">
         <v>820</v>
       </c>
-      <c r="H35" s="15">
+      <c r="H35" s="10">
         <v>0</v>
       </c>
-      <c r="I35" s="15">
+      <c r="I35" s="10">
         <f t="shared" ref="I35" si="0">G35-H35</f>
         <v>820</v>
       </c>
-      <c r="J35" s="15" t="s">
+      <c r="J35" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="K35" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="L35" s="15" t="s">
+      <c r="K35" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L35" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="N35" s="15" t="s">
+      <c r="N35" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="O35" s="15" t="s">
+      <c r="O35" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="P35" s="15" t="s">
+      <c r="P35" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="Q35" s="15">
+      <c r="Q35" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D37" s="8">
+      <c r="D37" s="1">
         <f>COUNTA(D3:D34)</f>
         <v>29</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="1">
         <f>SUBTOTAL(9,G3:G35)</f>
         <v>17625</v>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="1">
         <f t="shared" ref="H37:Q37" si="1">SUBTOTAL(9,H3:H35)</f>
         <v>875</v>
       </c>
-      <c r="I37" s="8">
+      <c r="I37" s="1">
         <f t="shared" si="1"/>
         <v>16750</v>
       </c>
-      <c r="J37" s="8">
+      <c r="J37" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K37" s="8">
+      <c r="K37" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L37" s="8">
+      <c r="L37" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M37" s="8">
+      <c r="M37" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N37" s="8">
+      <c r="N37" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O37" s="8">
+      <c r="O37" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P37" s="8">
+      <c r="P37" s="1">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q37" s="8">
+      <c r="Q37" s="1">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
@@ -2336,30 +2336,30 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C39" s="5" t="s">
+      <c r="A39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="D39" s="5"/>
-      <c r="E39" s="9" t="s">
+      <c r="D39" s="13"/>
+      <c r="E39" s="4" t="s">
         <v>128</v>
       </c>
       <c r="H39">
         <f>-4*25</f>
         <v>-100</v>
       </c>
-      <c r="K39" s="10" t="s">
+      <c r="K39" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L39" s="10" t="s">
+      <c r="L39" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="M39" s="10" t="s">
+      <c r="M39" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="O39" s="9" t="s">
+      <c r="O39" s="4" t="s">
         <v>130</v>
       </c>
     </row>
@@ -2367,15 +2367,15 @@
       <c r="A40" t="s">
         <v>23</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="14">
         <f>SUMIFS(I$3:I$35,B$3:B$35,A$39,L$3:L$35,A$40)</f>
         <v>15930</v>
       </c>
-      <c r="D40" s="4"/>
-      <c r="E40" s="11">
+      <c r="D40" s="14"/>
+      <c r="E40" s="3">
         <f>SUMIFS(Q$3:Q$35,B$3:B$35,A$39,L$3:L$35,A$40)</f>
         <v>32</v>
       </c>
@@ -2406,13 +2406,13 @@
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="15">
         <v>0</v>
       </c>
-      <c r="D41" s="3"/>
+      <c r="D41" s="15"/>
       <c r="K41" t="s">
         <v>135</v>
       </c>
@@ -2420,7 +2420,7 @@
         <f>-SUMIFS(H$3:H$35,J$3:J$35,K$39)+M41*5</f>
         <v>-195</v>
       </c>
-      <c r="M41" s="7">
+      <c r="M41" s="6">
         <f>SUMIFS(Q$3:Q$35,J$3:J$35,K$39)-COUNTIFS(J$3:J$35,K$39,M$3:M$35,"*gộp*")</f>
         <v>9</v>
       </c>
@@ -2433,15 +2433,15 @@
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="15">
         <f>-SUMIFS(I$3:I$35,B$3:B$35,A$39,P$3:P$35,"xx",N$3:N$35,"x")</f>
         <v>-820</v>
       </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="12">
+      <c r="D42" s="15"/>
+      <c r="E42" s="2">
         <f>SUMIFS(Q$3:Q$35,B$3:B$35,A$39,P$3:P$35,"xx",N$3:N$35,"x")</f>
         <v>1</v>
       </c>
@@ -2457,19 +2457,19 @@
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43" s="13">
         <f>SUBTOTAL(9,C40:C42)</f>
         <v>15110</v>
       </c>
-      <c r="D43" s="5"/>
+      <c r="D43" s="13"/>
       <c r="E43">
         <f>E40</f>
         <v>32</v>
       </c>
-      <c r="K43" s="12" t="s">
+      <c r="K43" s="2" t="s">
         <v>140</v>
       </c>
       <c r="O43" t="s">
@@ -2481,56 +2481,56 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="K44" s="12" t="s">
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="K44" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="O44" s="9" t="s">
+      <c r="O44" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="P44" s="9">
+      <c r="P44" s="4">
         <f>SUBTOTAL(9,P40:P43)</f>
         <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="L45" s="14">
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="L45" s="9">
         <f>SUBTOTAL(9,L40:L44)</f>
         <v>1635</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="9">
         <f>M40</f>
         <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47" s="12">
         <f>C43+C44+C45</f>
         <v>15110</v>
       </c>
-      <c r="D47" s="1"/>
-      <c r="E47" s="8" t="s">
+      <c r="D47" s="12"/>
+      <c r="E47" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="K47" s="10" t="s">
+      <c r="K47" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L47" s="10" t="s">
+      <c r="L47" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="M47" s="10" t="s">
+      <c r="M47" s="7" t="s">
         <v>128</v>
       </c>
     </row>
@@ -2566,12 +2566,12 @@
       </c>
     </row>
     <row r="51" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K51" s="12" t="s">
+      <c r="K51" s="2" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="52" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K52" s="12" t="s">
+      <c r="K52" s="2" t="s">
         <v>143</v>
       </c>
       <c r="L52">
@@ -2579,23 +2579,23 @@
       </c>
     </row>
     <row r="53" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="L53" s="14">
+      <c r="L53" s="9">
         <f>SUBTOTAL(9,L48:L52)</f>
         <v>8854</v>
       </c>
-      <c r="M53" s="14">
+      <c r="M53" s="9">
         <f>M48</f>
         <v>15</v>
       </c>
     </row>
     <row r="55" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K55" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="L55" s="10" t="s">
+      <c r="K55" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L55" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="M55" s="10" t="s">
+      <c r="M55" s="7" t="s">
         <v>128</v>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
         <f>-SUMIFS(H$3:H$35,J$3:J$35,K$55)+M57*5</f>
         <v>-165</v>
       </c>
-      <c r="M57" s="7">
+      <c r="M57" s="6">
         <f>SUMIFS(Q$3:Q$35,J$3:J$35,K$55)-COUNTIFS(J$3:J$35,K$55,M$3:M$35,"*gộp*")</f>
         <v>8</v>
       </c>
@@ -2639,21 +2639,21 @@
       </c>
     </row>
     <row r="59" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K59" s="12" t="s">
+      <c r="K59" s="2" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="60" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K60" s="12" t="s">
+      <c r="K60" s="2" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="61" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="L61" s="14">
+      <c r="L61" s="9">
         <f>SUBTOTAL(9,L56:L60)</f>
         <v>4776</v>
       </c>
-      <c r="M61" s="14">
+      <c r="M61" s="9">
         <f>M56</f>
         <v>8</v>
       </c>
